--- a/SOLUTION/TRACKS/quick-challenge/mru-quick-challenge-solution.xlsx
+++ b/SOLUTION/TRACKS/quick-challenge/mru-quick-challenge-solution.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solution" sheetId="1" r:id="Rfca700e872e242d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summaries" sheetId="2" r:id="Rd34ce7af20f040b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clean" sheetId="3" r:id="R1479e7b627b046ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw" sheetId="4" r:id="Re3604cfe6b5f4be7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solution" sheetId="1" r:id="R373c3ac51b714d32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summaries" sheetId="2" r:id="R5dbcc603b6714d3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clean" sheetId="3" r:id="R073c6ac3bdb24ad7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw" sheetId="4" r:id="R23e5769d48b64cd5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -775,7 +775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8a580bd6ce9e4234"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R812ed56bdfe6411a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -805,7 +805,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R13d9edb62246424a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5ab85e0c12464876"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2580,7 +2580,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd295fabe6528438d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6861ef80e4d4ffd"/>
 </x:worksheet>
 </file>
 
@@ -13618,7 +13618,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbcd5d2973844a1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra958e113ab2f46c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13730,7 +13730,7 @@
     </x:row>
     <x:row r="5" ht="23" customHeight="1">
       <x:c r="A5" s="18" t="str">
-        <x:v>Hourly value source: https://github.com/GlassHouse97/AI-Cost-Efficiency-Portfolio-Project/blob/main/QUESTIONS/TRACKS/quick-challenge/FORMULAS.md</x:v>
+        <x:v>Hourly value source: https://github.com/GlassHouse97/AI-Cost-Efficiency-Portfolio-Project/blob/main/QUESTIONS/TRACKS/quick-challenge/README.md</x:v>
       </x:c>
       <x:c r="B5" s="3"/>
       <x:c r="C5" s="3"/>
@@ -20271,7 +20271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re94a307ba16c484c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65d8781ede1b4148"/>
   </x:tableParts>
 </x:worksheet>
 </file>